--- a/pla.xlsx
+++ b/pla.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\sigabases-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB39784B-7E28-4810-B04B-21BF4113550B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD43B760-9A7C-450E-BE02-444453CF1850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62021AFD-8DCA-463E-B4DB-F4D8ED1C42DF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4055" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4057" uniqueCount="314">
   <si>
     <t>REGIONAL</t>
   </si>
@@ -978,6 +978,9 @@
   </si>
   <si>
     <t>PRATA</t>
+  </si>
+  <si>
+    <t>NOTA_PROJ</t>
   </si>
 </sst>
 </file>
@@ -1349,10 +1352,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A46FB2CD-C82C-4BE2-AAE2-71B506F2E290}">
-  <dimension ref="A1:I579"/>
+  <dimension ref="A1:J579"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1380,8 +1383,11 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1409,8 +1415,11 @@
       <c r="I2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J2">
+        <v>430142560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1438,8 +1447,11 @@
       <c r="I3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J3">
+        <v>430119742</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1467,8 +1479,11 @@
       <c r="I4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J4">
+        <v>430116805</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1496,8 +1511,11 @@
       <c r="I5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J5">
+        <v>430140862</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1525,8 +1543,11 @@
       <c r="I6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J6">
+        <v>430122695</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1554,8 +1575,11 @@
       <c r="I7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J7">
+        <v>430128668</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1583,8 +1607,11 @@
       <c r="I8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J8">
+        <v>430097762</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1612,8 +1639,11 @@
       <c r="I9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J9">
+        <v>430148605</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1642,7 +1672,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1671,7 +1701,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1699,8 +1729,11 @@
       <c r="I12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J12">
+        <v>430113400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1728,8 +1761,11 @@
       <c r="I13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J13">
+        <v>430118702</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1757,8 +1793,11 @@
       <c r="I14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J14">
+        <v>430137255</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -1786,8 +1825,11 @@
       <c r="I15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J15">
+        <v>430154152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1815,8 +1857,11 @@
       <c r="I16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J16">
+        <v>430125181</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -1844,8 +1889,11 @@
       <c r="I17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J17">
+        <v>430106389</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1873,8 +1921,11 @@
       <c r="I18" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J18">
+        <v>430148159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1902,8 +1953,11 @@
       <c r="I19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J19">
+        <v>430150391</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1932,7 +1986,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1961,7 +2015,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -1989,8 +2043,11 @@
       <c r="I22" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J22">
+        <v>430113111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -2019,7 +2076,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -2047,8 +2104,11 @@
       <c r="I24" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J24">
+        <v>430110540</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -2077,7 +2137,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -2106,7 +2166,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -2135,7 +2195,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -2163,8 +2223,11 @@
       <c r="I28" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J28">
+        <v>430128511</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -2193,7 +2256,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -2221,8 +2284,11 @@
       <c r="I30" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J30">
+        <v>430154572</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -2250,8 +2316,11 @@
       <c r="I31" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J31">
+        <v>430114576</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -2280,7 +2349,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -2308,8 +2377,11 @@
       <c r="I33" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J33">
+        <v>430113084</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -2337,8 +2409,11 @@
       <c r="I34" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J34">
+        <v>430112749</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -2366,8 +2441,11 @@
       <c r="I35" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J35">
+        <v>430113711</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -2395,8 +2473,11 @@
       <c r="I36" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J36">
+        <v>430118521</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -2424,8 +2505,11 @@
       <c r="I37" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J37">
+        <v>430114579</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -2453,8 +2537,11 @@
       <c r="I38" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J38">
+        <v>430116891</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -2482,8 +2569,11 @@
       <c r="I39" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J39">
+        <v>430113498</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -2511,8 +2601,11 @@
       <c r="I40" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J40">
+        <v>430122463</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -2540,8 +2633,11 @@
       <c r="I41" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J41">
+        <v>430124891</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -2569,8 +2665,11 @@
       <c r="I42" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J42">
+        <v>430148203</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -2598,8 +2697,11 @@
       <c r="I43" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J43">
+        <v>430150922</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -2628,7 +2730,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -2657,7 +2759,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -2685,8 +2787,11 @@
       <c r="I46" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J46">
+        <v>430114754</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>9</v>
       </c>
@@ -2714,8 +2819,11 @@
       <c r="I47" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J47">
+        <v>430115047</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>9</v>
       </c>
@@ -2743,8 +2851,11 @@
       <c r="I48" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J48">
+        <v>430115096</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>9</v>
       </c>
@@ -2773,7 +2884,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -2801,8 +2912,11 @@
       <c r="I50" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J50">
+        <v>430116077</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -2830,8 +2944,11 @@
       <c r="I51" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J51">
+        <v>430114993</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -2860,7 +2977,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -2889,7 +3006,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -2917,8 +3034,11 @@
       <c r="I54" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J54">
+        <v>430112688</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -2946,8 +3066,11 @@
       <c r="I55" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J55">
+        <v>430116590</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -2976,7 +3099,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -3004,8 +3127,11 @@
       <c r="I57" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J57">
+        <v>430120515</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -3033,8 +3159,11 @@
       <c r="I58" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J58">
+        <v>430116576</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>9</v>
       </c>
@@ -3062,8 +3191,11 @@
       <c r="I59" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J59">
+        <v>430117149</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>9</v>
       </c>
@@ -3091,8 +3223,11 @@
       <c r="I60" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J60">
+        <v>430118146</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -3121,7 +3256,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -3149,8 +3284,11 @@
       <c r="I62" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J62">
+        <v>430118276</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -3179,7 +3317,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>9</v>
       </c>
@@ -3207,8 +3345,11 @@
       <c r="I64" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J64">
+        <v>430076539</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>9</v>
       </c>
@@ -3236,8 +3377,11 @@
       <c r="I65" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J65">
+        <v>430117935</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>9</v>
       </c>
@@ -3265,8 +3409,11 @@
       <c r="I66" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J66">
+        <v>430118265</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>9</v>
       </c>
@@ -3294,8 +3441,11 @@
       <c r="I67" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J67">
+        <v>430115175</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -3323,8 +3473,11 @@
       <c r="I68" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J68">
+        <v>430115192</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -3352,8 +3505,11 @@
       <c r="I69" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J69">
+        <v>430119949</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>9</v>
       </c>
@@ -3381,8 +3537,11 @@
       <c r="I70" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J70">
+        <v>430141289</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>9</v>
       </c>
@@ -3411,7 +3570,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -3439,8 +3598,11 @@
       <c r="I72" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J72">
+        <v>430118306</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>9</v>
       </c>
@@ -3469,7 +3631,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -3497,8 +3659,11 @@
       <c r="I74" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J74">
+        <v>430119642</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>9</v>
       </c>
@@ -3526,8 +3691,11 @@
       <c r="I75" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J75">
+        <v>430119299</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>9</v>
       </c>
@@ -3555,8 +3723,11 @@
       <c r="I76" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J76">
+        <v>430118241</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>9</v>
       </c>
@@ -3584,8 +3755,11 @@
       <c r="I77" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J77">
+        <v>430119567</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>9</v>
       </c>
@@ -3613,8 +3787,11 @@
       <c r="I78" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J78">
+        <v>430044813</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>9</v>
       </c>
@@ -3642,8 +3819,11 @@
       <c r="I79" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J79">
+        <v>430113107</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>9</v>
       </c>
@@ -3671,8 +3851,11 @@
       <c r="I80" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J80">
+        <v>430115390</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -3700,8 +3883,11 @@
       <c r="I81" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J81">
+        <v>430123169</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>9</v>
       </c>
@@ -3729,8 +3915,11 @@
       <c r="I82" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J82">
+        <v>430116798</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>9</v>
       </c>
@@ -3758,8 +3947,11 @@
       <c r="I83" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J83">
+        <v>430119620</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>9</v>
       </c>
@@ -3787,8 +3979,11 @@
       <c r="I84" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J84">
+        <v>430118420</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>9</v>
       </c>
@@ -3816,8 +4011,11 @@
       <c r="I85" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J85">
+        <v>430120645</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>9</v>
       </c>
@@ -3845,8 +4043,11 @@
       <c r="I86" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J86">
+        <v>430120096</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>9</v>
       </c>
@@ -3874,8 +4075,11 @@
       <c r="I87" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J87">
+        <v>430123119</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>9</v>
       </c>
@@ -3903,8 +4107,11 @@
       <c r="I88" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J88">
+        <v>430093254</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>9</v>
       </c>
@@ -3932,8 +4139,11 @@
       <c r="I89" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J89">
+        <v>430122598</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>9</v>
       </c>
@@ -3961,8 +4171,11 @@
       <c r="I90" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J90">
+        <v>430113394</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>9</v>
       </c>
@@ -3990,8 +4203,11 @@
       <c r="I91" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J91">
+        <v>430122626</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>9</v>
       </c>
@@ -4019,8 +4235,11 @@
       <c r="I92" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J92">
+        <v>430125551</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>9</v>
       </c>
@@ -4048,8 +4267,11 @@
       <c r="I93" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J93">
+        <v>430130523</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>9</v>
       </c>
@@ -4077,8 +4299,11 @@
       <c r="I94" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J94">
+        <v>430122728</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>9</v>
       </c>
@@ -4106,8 +4331,11 @@
       <c r="I95" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J95">
+        <v>430130231</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>9</v>
       </c>
@@ -4135,8 +4363,11 @@
       <c r="I96" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J96">
+        <v>430143597</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>9</v>
       </c>
@@ -4164,8 +4395,11 @@
       <c r="I97" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J97">
+        <v>430122430</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>9</v>
       </c>
@@ -4193,8 +4427,11 @@
       <c r="I98" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J98">
+        <v>430123062</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>9</v>
       </c>
@@ -4222,8 +4459,11 @@
       <c r="I99" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J99">
+        <v>430122804</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>9</v>
       </c>
@@ -4251,8 +4491,11 @@
       <c r="I100" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J100">
+        <v>430078607</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>9</v>
       </c>
@@ -4280,8 +4523,11 @@
       <c r="I101" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J101">
+        <v>430130035</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>9</v>
       </c>
@@ -4309,8 +4555,11 @@
       <c r="I102" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J102">
+        <v>430121737</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>9</v>
       </c>
@@ -4338,8 +4587,11 @@
       <c r="I103" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J103">
+        <v>430130188</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>9</v>
       </c>
@@ -4367,8 +4619,11 @@
       <c r="I104" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J104">
+        <v>430140179</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>9</v>
       </c>
@@ -4396,8 +4651,11 @@
       <c r="I105" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J105">
+        <v>430137361</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>9</v>
       </c>
@@ -4425,8 +4683,11 @@
       <c r="I106" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J106">
+        <v>430101581</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>9</v>
       </c>
@@ -4454,8 +4715,11 @@
       <c r="I107" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J107">
+        <v>430148614</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>9</v>
       </c>
@@ -4483,8 +4747,11 @@
       <c r="I108" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J108">
+        <v>430140185</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -4512,8 +4779,11 @@
       <c r="I109" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J109">
+        <v>430140742</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>9</v>
       </c>
@@ -4541,8 +4811,11 @@
       <c r="I110" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J110">
+        <v>430125637</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>9</v>
       </c>
@@ -4570,8 +4843,11 @@
       <c r="I111" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J111">
+        <v>430141117</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>9</v>
       </c>
@@ -4599,8 +4875,11 @@
       <c r="I112" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J112">
+        <v>430123532</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>9</v>
       </c>
@@ -4628,8 +4907,11 @@
       <c r="I113" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J113">
+        <v>430141961</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>9</v>
       </c>
@@ -4657,8 +4939,11 @@
       <c r="I114" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J114">
+        <v>430148919</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>9</v>
       </c>
@@ -4686,8 +4971,11 @@
       <c r="I115" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J115">
+        <v>430123608</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>9</v>
       </c>
@@ -4715,8 +5003,11 @@
       <c r="I116" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J116">
+        <v>430123666</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>9</v>
       </c>
@@ -4744,8 +5035,11 @@
       <c r="I117" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J117">
+        <v>430128902</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>9</v>
       </c>
@@ -4774,7 +5068,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>9</v>
       </c>
@@ -4803,7 +5097,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>9</v>
       </c>
@@ -4832,7 +5126,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>9</v>
       </c>
@@ -4860,8 +5154,11 @@
       <c r="I121" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J121">
+        <v>430125101</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>9</v>
       </c>
@@ -4889,8 +5186,11 @@
       <c r="I122" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J122">
+        <v>430124565</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>9</v>
       </c>
@@ -4918,8 +5218,11 @@
       <c r="I123" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J123">
+        <v>430125086</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>9</v>
       </c>
@@ -4948,7 +5251,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>9</v>
       </c>
@@ -4976,8 +5279,11 @@
       <c r="I125" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J125">
+        <v>430128646</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>9</v>
       </c>
@@ -5005,8 +5311,11 @@
       <c r="I126" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J126">
+        <v>430125232</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>9</v>
       </c>
@@ -5035,7 +5344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>9</v>
       </c>
@@ -5064,7 +5373,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>9</v>
       </c>
@@ -5093,7 +5402,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -5121,8 +5430,11 @@
       <c r="I130" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J130">
+        <v>430132811</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>9</v>
       </c>
@@ -5150,8 +5462,11 @@
       <c r="I131" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J131">
+        <v>430129183</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>9</v>
       </c>
@@ -5179,8 +5494,11 @@
       <c r="I132" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J132">
+        <v>430128297</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>9</v>
       </c>
@@ -5208,8 +5526,11 @@
       <c r="I133" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J133">
+        <v>430093316</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>9</v>
       </c>
@@ -5237,8 +5558,11 @@
       <c r="I134" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J134">
+        <v>430126463</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -5267,7 +5591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>9</v>
       </c>
@@ -5296,7 +5620,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>9</v>
       </c>
@@ -5324,8 +5648,11 @@
       <c r="I137" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J137">
+        <v>430128666</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>9</v>
       </c>
@@ -5353,8 +5680,11 @@
       <c r="I138" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J138">
+        <v>430130401</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>9</v>
       </c>
@@ -5382,8 +5712,11 @@
       <c r="I139" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J139">
+        <v>430130082</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>9</v>
       </c>
@@ -5411,8 +5744,11 @@
       <c r="I140" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J140">
+        <v>430130081</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>9</v>
       </c>
@@ -5440,8 +5776,11 @@
       <c r="I141" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J141">
+        <v>430130381</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>9</v>
       </c>
@@ -5470,7 +5809,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>9</v>
       </c>
@@ -5498,8 +5837,11 @@
       <c r="I143" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J143">
+        <v>430032796</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>9</v>
       </c>
@@ -5528,7 +5870,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>9</v>
       </c>
@@ -5556,8 +5898,11 @@
       <c r="I145" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J145">
+        <v>430132202</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>9</v>
       </c>
@@ -5586,7 +5931,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>9</v>
       </c>
@@ -5614,8 +5959,11 @@
       <c r="I147" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J147">
+        <v>430130516</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>9</v>
       </c>
@@ -5643,8 +5991,11 @@
       <c r="I148" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J148">
+        <v>430130552</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>9</v>
       </c>
@@ -5672,8 +6023,11 @@
       <c r="I149" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J149">
+        <v>430130780</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>9</v>
       </c>
@@ -5702,7 +6056,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>9</v>
       </c>
@@ -5730,8 +6084,11 @@
       <c r="I151" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J151">
+        <v>430132102</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>9</v>
       </c>
@@ -5759,8 +6116,11 @@
       <c r="I152" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J152">
+        <v>430134938</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>9</v>
       </c>
@@ -5789,7 +6149,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>9</v>
       </c>
@@ -5818,7 +6178,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>9</v>
       </c>
@@ -5847,7 +6207,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>9</v>
       </c>
@@ -5876,7 +6236,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>9</v>
       </c>
@@ -5904,8 +6264,11 @@
       <c r="I157" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J157">
+        <v>430134941</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>9</v>
       </c>
@@ -5934,7 +6297,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>9</v>
       </c>
@@ -5963,7 +6326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>9</v>
       </c>
@@ -5991,8 +6354,11 @@
       <c r="I160" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J160">
+        <v>430132422</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>9</v>
       </c>
@@ -6021,7 +6387,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>9</v>
       </c>
@@ -6050,7 +6416,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>9</v>
       </c>
@@ -6078,8 +6444,11 @@
       <c r="I163" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J163">
+        <v>430135001</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>9</v>
       </c>
@@ -6107,8 +6476,11 @@
       <c r="I164" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J164">
+        <v>430135252</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>9</v>
       </c>
@@ -6136,8 +6508,11 @@
       <c r="I165" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J165">
+        <v>430135797</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>9</v>
       </c>
@@ -6165,8 +6540,11 @@
       <c r="I166" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J166">
+        <v>430134988</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>9</v>
       </c>
@@ -6194,8 +6572,11 @@
       <c r="I167" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J167">
+        <v>430137530</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>9</v>
       </c>
@@ -6223,8 +6604,11 @@
       <c r="I168" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J168">
+        <v>430135614</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>9</v>
       </c>
@@ -6253,7 +6637,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>9</v>
       </c>
@@ -6281,8 +6665,11 @@
       <c r="I170" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J170">
+        <v>430120044</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>9</v>
       </c>
@@ -6310,8 +6697,11 @@
       <c r="I171" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J171">
+        <v>430135852</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>9</v>
       </c>
@@ -6339,8 +6729,11 @@
       <c r="I172" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J172">
+        <v>430125334</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>9</v>
       </c>
@@ -6368,8 +6761,11 @@
       <c r="I173" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J173">
+        <v>430128944</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>9</v>
       </c>
@@ -6397,8 +6793,11 @@
       <c r="I174" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J174">
+        <v>430137377</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>9</v>
       </c>
@@ -6426,8 +6825,11 @@
       <c r="I175" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J175">
+        <v>430095231</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>9</v>
       </c>
@@ -6455,8 +6857,11 @@
       <c r="I176" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J176">
+        <v>430149905</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>9</v>
       </c>
@@ -6485,7 +6890,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>9</v>
       </c>
@@ -6513,8 +6918,11 @@
       <c r="I178" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J178">
+        <v>430136489</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>9</v>
       </c>
@@ -6542,8 +6950,11 @@
       <c r="I179" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J179">
+        <v>430136781</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>9</v>
       </c>
@@ -6571,8 +6982,11 @@
       <c r="I180" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J180">
+        <v>430061212</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>9</v>
       </c>
@@ -6600,8 +7014,11 @@
       <c r="I181" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J181">
+        <v>430136454</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>9</v>
       </c>
@@ -6629,8 +7046,11 @@
       <c r="I182" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J182">
+        <v>430111577</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>9</v>
       </c>
@@ -6658,8 +7078,11 @@
       <c r="I183" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J183">
+        <v>430132171</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>9</v>
       </c>
@@ -6687,8 +7110,11 @@
       <c r="I184" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J184">
+        <v>430142137</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>9</v>
       </c>
@@ -6716,8 +7142,11 @@
       <c r="I185" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J185">
+        <v>430137182</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>9</v>
       </c>
@@ -6745,8 +7174,11 @@
       <c r="I186" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J186" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>9</v>
       </c>
@@ -6774,8 +7206,11 @@
       <c r="I187" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J187">
+        <v>430148230</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>9</v>
       </c>
@@ -6803,8 +7238,11 @@
       <c r="I188" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J188">
+        <v>430138855</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>9</v>
       </c>
@@ -6832,8 +7270,11 @@
       <c r="I189" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J189">
+        <v>430148221</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>9</v>
       </c>
@@ -6861,8 +7302,11 @@
       <c r="I190" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J190">
+        <v>430139390</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>9</v>
       </c>
@@ -6891,7 +7335,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>9</v>
       </c>
@@ -6919,8 +7363,11 @@
       <c r="I192" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J192">
+        <v>430152686</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>9</v>
       </c>
@@ -6949,7 +7396,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>9</v>
       </c>
@@ -6977,8 +7424,11 @@
       <c r="I194" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J194">
+        <v>430139388</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>9</v>
       </c>
@@ -7006,8 +7456,11 @@
       <c r="I195" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J195">
+        <v>430139131</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>9</v>
       </c>
@@ -7035,8 +7488,11 @@
       <c r="I196" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J196">
+        <v>430138840</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>9</v>
       </c>
@@ -7064,8 +7520,11 @@
       <c r="I197" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J197">
+        <v>430138767</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>9</v>
       </c>
@@ -7093,8 +7552,11 @@
       <c r="I198" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J198">
+        <v>430121031</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>9</v>
       </c>
@@ -7122,8 +7584,11 @@
       <c r="I199" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J199">
+        <v>430140376</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>9</v>
       </c>
@@ -7151,8 +7616,11 @@
       <c r="I200" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J200">
+        <v>430113701</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>9</v>
       </c>
@@ -7180,8 +7648,11 @@
       <c r="I201" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J201">
+        <v>430113394</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>9</v>
       </c>
@@ -7209,8 +7680,11 @@
       <c r="I202" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J202">
+        <v>430140916</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>9</v>
       </c>
@@ -7238,8 +7712,11 @@
       <c r="I203" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J203">
+        <v>430140087</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>9</v>
       </c>
@@ -7267,8 +7744,11 @@
       <c r="I204" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J204">
+        <v>430140064</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>9</v>
       </c>
@@ -7296,8 +7776,11 @@
       <c r="I205" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J205">
+        <v>430119901</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>9</v>
       </c>
@@ -7325,8 +7808,11 @@
       <c r="I206" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J206">
+        <v>430140504</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>9</v>
       </c>
@@ -7354,8 +7840,11 @@
       <c r="I207" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J207">
+        <v>430114053</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>9</v>
       </c>
@@ -7383,8 +7872,11 @@
       <c r="I208" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J208">
+        <v>430150662</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>9</v>
       </c>
@@ -7412,8 +7904,11 @@
       <c r="I209" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J209">
+        <v>430132100</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>9</v>
       </c>
@@ -7441,8 +7936,11 @@
       <c r="I210" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J210">
+        <v>430141492</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>9</v>
       </c>
@@ -7470,8 +7968,11 @@
       <c r="I211" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J211">
+        <v>430135690</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>9</v>
       </c>
@@ -7500,7 +8001,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>9</v>
       </c>
@@ -7528,8 +8029,11 @@
       <c r="I213" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J213">
+        <v>430148157</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>9</v>
       </c>
@@ -7557,8 +8061,11 @@
       <c r="I214" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J214">
+        <v>430122816</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>9</v>
       </c>
@@ -7586,8 +8093,11 @@
       <c r="I215" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J215">
+        <v>430150073</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>9</v>
       </c>
@@ -7615,8 +8125,11 @@
       <c r="I216" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J216">
+        <v>430150403</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>9</v>
       </c>
@@ -7644,8 +8157,11 @@
       <c r="I217" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J217">
+        <v>430149693</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>9</v>
       </c>
@@ -7673,8 +8189,11 @@
       <c r="I218" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J218">
+        <v>430142143</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>9</v>
       </c>
@@ -7702,8 +8221,11 @@
       <c r="I219" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J219">
+        <v>430150292</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>9</v>
       </c>
@@ -7731,8 +8253,11 @@
       <c r="I220" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J220">
+        <v>430137131</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>9</v>
       </c>
@@ -7760,8 +8285,11 @@
       <c r="I221" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J221">
+        <v>430153626</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>9</v>
       </c>
@@ -7789,8 +8317,11 @@
       <c r="I222" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J222">
+        <v>430149886</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>9</v>
       </c>
@@ -7818,8 +8349,11 @@
       <c r="I223" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J223">
+        <v>430151443</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>9</v>
       </c>
@@ -7847,8 +8381,11 @@
       <c r="I224" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J224">
+        <v>430155084</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>9</v>
       </c>
@@ -7876,8 +8413,11 @@
       <c r="I225" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J225">
+        <v>430154518</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>9</v>
       </c>
@@ -7906,7 +8446,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>9</v>
       </c>
@@ -7934,8 +8474,11 @@
       <c r="I227" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J227">
+        <v>430153713</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>9</v>
       </c>
@@ -7963,8 +8506,11 @@
       <c r="I228" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J228">
+        <v>430154493</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>9</v>
       </c>
@@ -7992,8 +8538,11 @@
       <c r="I229" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J229">
+        <v>430151743</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>9</v>
       </c>
@@ -8021,8 +8570,11 @@
       <c r="I230" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J230">
+        <v>430153113</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>9</v>
       </c>
@@ -8050,8 +8602,11 @@
       <c r="I231" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J231">
+        <v>430149883</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>9</v>
       </c>
@@ -8080,7 +8635,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>9</v>
       </c>
@@ -8108,8 +8663,11 @@
       <c r="I233" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J233">
+        <v>430151005</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>9</v>
       </c>
@@ -8137,8 +8695,11 @@
       <c r="I234" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J234">
+        <v>430155227</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>9</v>
       </c>
@@ -8166,8 +8727,11 @@
       <c r="I235" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J235">
+        <v>430140892</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>9</v>
       </c>
@@ -8196,7 +8760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>9</v>
       </c>
@@ -8225,7 +8789,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>9</v>
       </c>
@@ -8253,8 +8817,11 @@
       <c r="I238" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J238">
+        <v>430119761</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>9</v>
       </c>
@@ -8282,8 +8849,11 @@
       <c r="I239" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J239">
+        <v>430122504</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>9</v>
       </c>
@@ -8311,8 +8881,11 @@
       <c r="I240" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J240">
+        <v>430114004</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>9</v>
       </c>
@@ -8340,8 +8913,11 @@
       <c r="I241" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J241">
+        <v>430125942</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>9</v>
       </c>
@@ -8369,8 +8945,11 @@
       <c r="I242" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J242">
+        <v>430107971</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>9</v>
       </c>
@@ -8398,8 +8977,11 @@
       <c r="I243" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J243">
+        <v>430108425</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>9</v>
       </c>
@@ -8427,8 +9009,11 @@
       <c r="I244" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J244">
+        <v>430128469</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>9</v>
       </c>
@@ -8456,8 +9041,11 @@
       <c r="I245" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J245">
+        <v>430109520</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>9</v>
       </c>
@@ -8485,8 +9073,11 @@
       <c r="I246" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J246">
+        <v>430130806</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>9</v>
       </c>
@@ -8514,8 +9105,11 @@
       <c r="I247" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J247">
+        <v>430111714</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>9</v>
       </c>
@@ -8543,8 +9137,11 @@
       <c r="I248" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J248">
+        <v>430116531</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>9</v>
       </c>
@@ -8572,8 +9169,11 @@
       <c r="I249" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J249">
+        <v>430140008</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>9</v>
       </c>
@@ -8601,8 +9201,11 @@
       <c r="I250" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J250">
+        <v>430142246</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>9</v>
       </c>
@@ -8630,8 +9233,11 @@
       <c r="I251" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J251">
+        <v>430142481</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>9</v>
       </c>
@@ -8659,8 +9265,11 @@
       <c r="I252" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J252">
+        <v>430114926</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>9</v>
       </c>
@@ -8688,8 +9297,11 @@
       <c r="I253" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J253">
+        <v>430114926</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>9</v>
       </c>
@@ -8717,8 +9329,11 @@
       <c r="I254" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J254">
+        <v>430154172</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>9</v>
       </c>
@@ -8746,8 +9361,11 @@
       <c r="I255" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J255">
+        <v>430116446</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>9</v>
       </c>
@@ -8775,8 +9393,11 @@
       <c r="I256" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J256">
+        <v>430118273</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>9</v>
       </c>
@@ -8804,8 +9425,11 @@
       <c r="I257" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J257">
+        <v>430123286</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>9</v>
       </c>
@@ -8833,8 +9457,11 @@
       <c r="I258" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J258">
+        <v>430150788</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>9</v>
       </c>
@@ -8862,8 +9489,11 @@
       <c r="I259" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J259">
+        <v>430124002</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>9</v>
       </c>
@@ -8891,8 +9521,11 @@
       <c r="I260" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J260">
+        <v>430125241</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>9</v>
       </c>
@@ -8920,8 +9553,11 @@
       <c r="I261" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J261">
+        <v>430134963</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>9</v>
       </c>
@@ -8949,8 +9585,11 @@
       <c r="I262" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J262">
+        <v>430136671</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>9</v>
       </c>
@@ -8978,8 +9617,11 @@
       <c r="I263" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J263">
+        <v>430137150</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>9</v>
       </c>
@@ -9008,7 +9650,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>9</v>
       </c>
@@ -9037,7 +9679,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>9</v>
       </c>
@@ -9066,7 +9708,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>9</v>
       </c>
@@ -9095,7 +9737,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>9</v>
       </c>
@@ -9124,7 +9766,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>9</v>
       </c>
@@ -9153,7 +9795,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>9</v>
       </c>
@@ -9181,8 +9823,11 @@
       <c r="I270" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J270">
+        <v>430101604</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>9</v>
       </c>
@@ -9211,7 +9856,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>9</v>
       </c>
@@ -9240,7 +9885,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>9</v>
       </c>
@@ -9269,7 +9914,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>9</v>
       </c>
@@ -9298,7 +9943,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>9</v>
       </c>
@@ -9327,7 +9972,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>9</v>
       </c>
@@ -9355,8 +10000,11 @@
       <c r="I276" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J276">
+        <v>430128404</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>9</v>
       </c>
@@ -9385,7 +10033,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>9</v>
       </c>
@@ -9414,7 +10062,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>9</v>
       </c>
@@ -9443,7 +10091,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>9</v>
       </c>
@@ -9472,7 +10120,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>9</v>
       </c>
@@ -9501,7 +10149,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>9</v>
       </c>
@@ -9530,7 +10178,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>9</v>
       </c>
@@ -9559,7 +10207,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>9</v>
       </c>
@@ -9588,7 +10236,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>9</v>
       </c>
@@ -9617,7 +10265,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>9</v>
       </c>
@@ -9646,7 +10294,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>9</v>
       </c>
@@ -9675,7 +10323,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>9</v>
       </c>
@@ -9704,7 +10352,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>9</v>
       </c>
@@ -9733,7 +10381,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>9</v>
       </c>
@@ -9762,7 +10410,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>9</v>
       </c>
@@ -9791,7 +10439,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>9</v>
       </c>
@@ -9820,7 +10468,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>9</v>
       </c>
@@ -9849,7 +10497,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>9</v>
       </c>
@@ -9878,7 +10526,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>9</v>
       </c>
@@ -9907,7 +10555,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>9</v>
       </c>
@@ -9936,7 +10584,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>9</v>
       </c>
@@ -9965,7 +10613,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>9</v>
       </c>
@@ -9993,8 +10641,11 @@
       <c r="I298" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J298">
+        <v>430137206</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>9</v>
       </c>
@@ -10023,7 +10674,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>9</v>
       </c>
@@ -10051,8 +10702,11 @@
       <c r="I300" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J300">
+        <v>430117283</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>9</v>
       </c>
@@ -10081,7 +10735,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>9</v>
       </c>
@@ -10109,8 +10763,11 @@
       <c r="I302" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J302">
+        <v>430104983</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>9</v>
       </c>
@@ -10139,7 +10796,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>9</v>
       </c>
@@ -10168,7 +10825,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>9</v>
       </c>
@@ -10197,7 +10854,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>9</v>
       </c>
@@ -10226,7 +10883,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>9</v>
       </c>
@@ -10255,7 +10912,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>9</v>
       </c>
@@ -10284,7 +10941,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>9</v>
       </c>
@@ -10312,8 +10969,11 @@
       <c r="I309" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J309">
+        <v>430121299</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>9</v>
       </c>
@@ -10342,7 +11002,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>9</v>
       </c>
@@ -10371,7 +11031,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>9</v>
       </c>
@@ -10400,7 +11060,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>9</v>
       </c>
@@ -10429,7 +11089,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>9</v>
       </c>
@@ -10457,8 +11117,11 @@
       <c r="I314" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J314">
+        <v>430124389</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>9</v>
       </c>
@@ -10486,8 +11149,11 @@
       <c r="I315" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J315">
+        <v>430110848</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>9</v>
       </c>
@@ -10515,8 +11181,11 @@
       <c r="I316" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J316">
+        <v>430113595</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>9</v>
       </c>
@@ -10545,7 +11214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>9</v>
       </c>
@@ -10573,8 +11242,11 @@
       <c r="I318" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J318">
+        <v>430124332</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>9</v>
       </c>
@@ -10602,8 +11274,11 @@
       <c r="I319" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J319">
+        <v>430135683</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>9</v>
       </c>
@@ -10632,7 +11307,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>9</v>
       </c>
@@ -10661,7 +11336,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>9</v>
       </c>
@@ -10689,8 +11364,11 @@
       <c r="I322" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J322">
+        <v>430132200</v>
+      </c>
+    </row>
+    <row r="323" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>9</v>
       </c>
@@ -10719,7 +11397,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>9</v>
       </c>
@@ -10748,7 +11426,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>9</v>
       </c>
@@ -10777,7 +11455,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>9</v>
       </c>
@@ -10806,7 +11484,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>9</v>
       </c>
@@ -10835,7 +11513,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>9</v>
       </c>
@@ -10864,7 +11542,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>9</v>
       </c>
@@ -10893,7 +11571,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>9</v>
       </c>
@@ -10922,7 +11600,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>9</v>
       </c>
@@ -10951,7 +11629,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>9</v>
       </c>
@@ -10980,7 +11658,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>9</v>
       </c>
@@ -11009,7 +11687,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>9</v>
       </c>
@@ -11038,7 +11716,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>9</v>
       </c>
@@ -11067,7 +11745,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>9</v>
       </c>
@@ -11096,7 +11774,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>9</v>
       </c>
@@ -11125,7 +11803,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>9</v>
       </c>
@@ -11153,8 +11831,11 @@
       <c r="I338" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J338">
+        <v>430129485</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>9</v>
       </c>
@@ -11183,7 +11864,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>9</v>
       </c>
@@ -11211,8 +11892,11 @@
       <c r="I340" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J340">
+        <v>430122739</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>9</v>
       </c>
@@ -11240,8 +11924,11 @@
       <c r="I341" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J341">
+        <v>430097135</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>9</v>
       </c>
@@ -11270,7 +11957,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>9</v>
       </c>
@@ -11299,7 +11986,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>9</v>
       </c>
@@ -11328,7 +12015,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>9</v>
       </c>
@@ -11357,7 +12044,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>9</v>
       </c>
@@ -11385,8 +12072,11 @@
       <c r="I346" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J346">
+        <v>430098944</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>9</v>
       </c>
@@ -11415,7 +12105,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>9</v>
       </c>
@@ -11444,7 +12134,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>9</v>
       </c>
@@ -11473,7 +12163,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>9</v>
       </c>
@@ -11501,8 +12191,11 @@
       <c r="I350" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J350">
+        <v>430132019</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>9</v>
       </c>
@@ -11530,8 +12223,11 @@
       <c r="I351" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J351">
+        <v>430150725</v>
+      </c>
+    </row>
+    <row r="352" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>9</v>
       </c>
@@ -11560,7 +12256,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>9</v>
       </c>
@@ -11588,8 +12284,11 @@
       <c r="I353" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J353">
+        <v>430153552</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>9</v>
       </c>
@@ -11618,7 +12317,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>9</v>
       </c>
@@ -11646,8 +12345,11 @@
       <c r="I355" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J355">
+        <v>430117292</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>9</v>
       </c>
@@ -11676,7 +12378,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>9</v>
       </c>
@@ -11705,7 +12407,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>9</v>
       </c>
@@ -11734,7 +12436,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>9</v>
       </c>
@@ -11763,7 +12465,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>9</v>
       </c>
@@ -11792,7 +12494,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>9</v>
       </c>
@@ -11821,7 +12523,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>9</v>
       </c>
@@ -11849,8 +12551,11 @@
       <c r="I362" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J362">
+        <v>430119714</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>9</v>
       </c>
@@ -11879,7 +12584,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>9</v>
       </c>
@@ -11907,8 +12612,11 @@
       <c r="I364" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J364">
+        <v>430119134</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>9</v>
       </c>
@@ -11936,8 +12644,11 @@
       <c r="I365" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J365">
+        <v>430132519</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>9</v>
       </c>
@@ -11966,7 +12677,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>9</v>
       </c>
@@ -11995,7 +12706,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>9</v>
       </c>
@@ -12023,8 +12734,11 @@
       <c r="I368" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J368">
+        <v>430150037</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>9</v>
       </c>
@@ -12053,7 +12767,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>9</v>
       </c>
@@ -12082,7 +12796,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>9</v>
       </c>
@@ -12111,7 +12825,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>9</v>
       </c>
@@ -12140,7 +12854,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>9</v>
       </c>
@@ -12169,7 +12883,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>9</v>
       </c>
@@ -12198,7 +12912,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>9</v>
       </c>
@@ -12227,7 +12941,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>9</v>
       </c>
@@ -12256,7 +12970,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>9</v>
       </c>
@@ -12285,7 +12999,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>9</v>
       </c>
@@ -12313,8 +13027,11 @@
       <c r="I378" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J378">
+        <v>430115198</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>9</v>
       </c>
@@ -12342,8 +13059,11 @@
       <c r="I379" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J379">
+        <v>430111942</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>9</v>
       </c>
@@ -12371,8 +13091,11 @@
       <c r="I380" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J380">
+        <v>430117178</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>9</v>
       </c>
@@ -12401,7 +13124,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>9</v>
       </c>
@@ -12430,7 +13153,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>9</v>
       </c>
@@ -12459,7 +13182,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>9</v>
       </c>
@@ -12488,7 +13211,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>9</v>
       </c>
@@ -12516,8 +13239,11 @@
       <c r="I385" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J385">
+        <v>430117818</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>9</v>
       </c>
@@ -12546,7 +13272,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>9</v>
       </c>
@@ -12574,8 +13300,11 @@
       <c r="I387" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J387">
+        <v>430117796</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>9</v>
       </c>
@@ -12604,7 +13333,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>9</v>
       </c>
@@ -12633,7 +13362,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>9</v>
       </c>
@@ -12662,7 +13391,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>9</v>
       </c>
@@ -12691,7 +13420,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>9</v>
       </c>
@@ -12720,7 +13449,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>9</v>
       </c>
@@ -12749,7 +13478,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>9</v>
       </c>
@@ -12778,7 +13507,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>9</v>
       </c>
@@ -12806,8 +13535,11 @@
       <c r="I395" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J395">
+        <v>430114019</v>
+      </c>
+    </row>
+    <row r="396" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>9</v>
       </c>
@@ -12835,8 +13567,11 @@
       <c r="I396" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J396">
+        <v>430113761</v>
+      </c>
+    </row>
+    <row r="397" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>9</v>
       </c>
@@ -12865,7 +13600,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>9</v>
       </c>
@@ -12894,7 +13629,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>9</v>
       </c>
@@ -12923,7 +13658,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>9</v>
       </c>
@@ -12952,7 +13687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>9</v>
       </c>
@@ -12981,7 +13716,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>9</v>
       </c>
@@ -13009,8 +13744,11 @@
       <c r="I402" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J402">
+        <v>430121237</v>
+      </c>
+    </row>
+    <row r="403" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>9</v>
       </c>
@@ -13039,7 +13777,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>9</v>
       </c>
@@ -13067,8 +13805,11 @@
       <c r="I404" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J404">
+        <v>430120774</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>9</v>
       </c>
@@ -13097,7 +13838,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>9</v>
       </c>
@@ -13126,7 +13867,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>9</v>
       </c>
@@ -13155,7 +13896,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>9</v>
       </c>
@@ -13184,7 +13925,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>9</v>
       </c>
@@ -13213,7 +13954,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>9</v>
       </c>
@@ -13241,8 +13982,11 @@
       <c r="I410" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J410">
+        <v>430122705</v>
+      </c>
+    </row>
+    <row r="411" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>9</v>
       </c>
@@ -13271,7 +14015,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>9</v>
       </c>
@@ -13299,8 +14043,11 @@
       <c r="I412" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J412">
+        <v>430123316</v>
+      </c>
+    </row>
+    <row r="413" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>9</v>
       </c>
@@ -13328,8 +14075,11 @@
       <c r="I413" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J413">
+        <v>430137640</v>
+      </c>
+    </row>
+    <row r="414" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>9</v>
       </c>
@@ -13358,7 +14108,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>9</v>
       </c>
@@ -13387,7 +14137,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>9</v>
       </c>
@@ -13415,8 +14165,11 @@
       <c r="I416" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J416">
+        <v>430141318</v>
+      </c>
+    </row>
+    <row r="417" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>9</v>
       </c>
@@ -13445,7 +14198,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>9</v>
       </c>
@@ -13473,8 +14226,11 @@
       <c r="I418" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J418">
+        <v>430148563</v>
+      </c>
+    </row>
+    <row r="419" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>9</v>
       </c>
@@ -13503,7 +14259,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>9</v>
       </c>
@@ -13532,7 +14288,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>9</v>
       </c>
@@ -13561,7 +14317,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>9</v>
       </c>
@@ -13589,8 +14345,11 @@
       <c r="I422" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J422">
+        <v>430137304</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>9</v>
       </c>
@@ -13619,7 +14378,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>9</v>
       </c>
@@ -13648,7 +14407,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>9</v>
       </c>
@@ -13676,8 +14435,11 @@
       <c r="I425" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J425">
+        <v>430149616</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>9</v>
       </c>
@@ -13705,8 +14467,11 @@
       <c r="I426" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J426">
+        <v>430119735</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>9</v>
       </c>
@@ -13735,7 +14500,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>9</v>
       </c>
@@ -13763,8 +14528,11 @@
       <c r="I428" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J428">
+        <v>430124853</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>9</v>
       </c>
@@ -13793,7 +14561,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>9</v>
       </c>
@@ -13821,8 +14589,11 @@
       <c r="I430" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J430">
+        <v>430131724</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>9</v>
       </c>
@@ -13850,8 +14621,11 @@
       <c r="I431" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J431">
+        <v>430148613</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>9</v>
       </c>
@@ -13879,6 +14653,9 @@
       <c r="I432" t="s">
         <v>23</v>
       </c>
+      <c r="J432">
+        <v>430148652</v>
+      </c>
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
@@ -14808,7 +15585,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>9</v>
       </c>
@@ -14837,7 +15614,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>9</v>
       </c>
@@ -14866,7 +15643,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>9</v>
       </c>
@@ -14895,7 +15672,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>9</v>
       </c>
@@ -14924,7 +15701,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>9</v>
       </c>
@@ -14953,7 +15730,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>9</v>
       </c>
@@ -14982,7 +15759,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>9</v>
       </c>
@@ -15011,7 +15788,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>9</v>
       </c>
@@ -15039,8 +15816,11 @@
       <c r="I472" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J472">
+        <v>430118324</v>
+      </c>
+    </row>
+    <row r="473" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>9</v>
       </c>
@@ -15068,8 +15848,11 @@
       <c r="I473" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J473">
+        <v>430118392</v>
+      </c>
+    </row>
+    <row r="474" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>9</v>
       </c>
@@ -15097,8 +15880,11 @@
       <c r="I474" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J474">
+        <v>430149149</v>
+      </c>
+    </row>
+    <row r="475" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>9</v>
       </c>
@@ -15127,7 +15913,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>9</v>
       </c>
@@ -15156,7 +15942,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>9</v>
       </c>
@@ -15185,7 +15971,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>9</v>
       </c>
@@ -15214,7 +16000,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>9</v>
       </c>
@@ -15243,7 +16029,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>9</v>
       </c>
